--- a/ЛР6_ЦП_Канвас_сценарии_релизы/Excel/ЛР6_3_бизнес_логика_и_сценарии_TableMind.xlsx
+++ b/ЛР6_ЦП_Канвас_сценарии_релизы/Excel/ЛР6_3_бизнес_логика_и_сценарии_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР6_ЦП_Канвас_сценарии_релизы\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР6_ЦП_Канвас_сценарии_релизы\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651B928A-1C1C-4631-927F-B513EA17E78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C1B1CF-0CE9-4596-AB85-E65FD42AE481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -1420,9 +1420,6 @@
     <t>Роль: аналитик</t>
   </si>
   <si>
-    <t>модельные бюджеты, нужен опрос</t>
-  </si>
-  <si>
     <t>A-012</t>
   </si>
   <si>
@@ -2267,6 +2264,9 @@
   </si>
   <si>
     <t>требует накопления правил</t>
+  </si>
+  <si>
+    <t>расчетные бюджеты, проверка по данным MVP</t>
   </si>
 </sst>
 </file>
@@ -5659,27 +5659,27 @@
         <v>Проверить дополнительно</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>458</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="17" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="G15" s="6">
         <v>3</v>
@@ -5698,14 +5698,14 @@
         <v>74</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M15" s="8" t="str">
         <f t="shared" si="1"/>
         <v>Проверить дополнительно</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="17" customHeight="1">
@@ -9679,7 +9679,7 @@
       <c r="H196" s="6"/>
       <c r="I196" s="6"/>
       <c r="J196" s="7">
-        <f t="shared" ref="J196:J227" si="12">IFERROR((G196*H196)*(6-I196)/20,"")</f>
+        <f t="shared" ref="J196:J203" si="12">IFERROR((G196*H196)*(6-I196)/20,"")</f>
         <v>0</v>
       </c>
       <c r="K196" s="4"/>
@@ -10000,19 +10000,19 @@
         <v>96</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>415</v>
@@ -10035,7 +10035,7 @@
         <v>98</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="17" customHeight="1">
@@ -10043,25 +10043,25 @@
         <v>99</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>326</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>423</v>
@@ -10084,33 +10084,33 @@
         <v>98</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="17" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>485</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>400</v>
@@ -10133,33 +10133,33 @@
         <v>98</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>488</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>408</v>
@@ -10182,33 +10182,33 @@
         <v>98</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="17" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>437</v>
@@ -10231,33 +10231,33 @@
         <v>98</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="17" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>429</v>
@@ -10280,7 +10280,7 @@
         <v>98</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="17" customHeight="1">
@@ -14578,7 +14578,7 @@
         <v/>
       </c>
       <c r="M196" s="7" t="str">
-        <f t="shared" ref="M196:M227" si="13">IF(A196="","",IFERROR(J196*K196*L196/20,0))</f>
+        <f t="shared" ref="M196:M203" si="13">IF(A196="","",IFERROR(J196*K196*L196/20,0))</f>
         <v/>
       </c>
       <c r="N196" s="4"/>
@@ -14895,19 +14895,19 @@
         <v>116</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="G4" s="4">
         <v>4</v>
@@ -14920,7 +14920,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>450</v>
@@ -14932,7 +14932,7 @@
         <v>3</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="17" customHeight="1">
@@ -14940,19 +14940,19 @@
         <v>118</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>523</v>
       </c>
       <c r="G5" s="4">
         <v>5</v>
@@ -14965,7 +14965,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>450</v>
@@ -14977,27 +14977,27 @@
         <v>3</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="17" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>530</v>
       </c>
       <c r="G6" s="4">
         <v>3</v>
@@ -15010,7 +15010,7 @@
         <v>12</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>450</v>
@@ -15027,22 +15027,22 @@
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -15055,13 +15055,13 @@
         <v>9</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>450</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M7" s="4">
         <v>2</v>
@@ -15072,22 +15072,22 @@
     </row>
     <row r="8" spans="1:26" ht="17" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="G8" s="4">
         <v>4</v>
@@ -15100,7 +15100,7 @@
         <v>8</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>296</v>
@@ -18678,7 +18678,7 @@
       <c r="G196" s="4"/>
       <c r="H196" s="4"/>
       <c r="I196" s="8" t="str">
-        <f t="shared" ref="I196:I227" si="6">IF(A196="","",IFERROR(G196*H196,""))</f>
+        <f t="shared" ref="I196:I203" si="6">IF(A196="","",IFERROR(G196*H196,""))</f>
         <v/>
       </c>
       <c r="J196" s="4"/>
@@ -18997,10 +18997,10 @@
         <v>136</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>137</v>
@@ -19009,28 +19009,28 @@
         <v>138</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="N4" s="4">
         <v>5</v>
@@ -19064,10 +19064,10 @@
         <v>139</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>147</v>
@@ -19076,28 +19076,28 @@
         <v>138</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>563</v>
       </c>
       <c r="N5" s="4">
         <v>5</v>
@@ -19128,13 +19128,13 @@
     </row>
     <row r="6" spans="1:26" ht="17" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>565</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>141</v>
@@ -19143,28 +19143,28 @@
         <v>142</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>573</v>
       </c>
       <c r="N6" s="4">
         <v>4</v>
@@ -19195,13 +19195,13 @@
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>575</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>141</v>
@@ -19210,28 +19210,28 @@
         <v>142</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="L7" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>582</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>583</v>
       </c>
       <c r="N7" s="4">
         <v>4</v>
@@ -19262,13 +19262,13 @@
     </row>
     <row r="8" spans="1:26" ht="17" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>585</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>137</v>
@@ -19277,28 +19277,28 @@
         <v>138</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>590</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>591</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>151</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="N8" s="4">
         <v>5</v>
@@ -19329,13 +19329,13 @@
     </row>
     <row r="9" spans="1:26" ht="17" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>137</v>
@@ -19344,28 +19344,28 @@
         <v>138</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>600</v>
-      </c>
       <c r="M9" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N9" s="4">
         <v>3</v>
@@ -19396,13 +19396,13 @@
     </row>
     <row r="10" spans="1:26" ht="17" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>602</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>137</v>
@@ -19411,28 +19411,28 @@
         <v>138</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>609</v>
-      </c>
       <c r="M10" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N10" s="4">
         <v>3</v>
@@ -19463,13 +19463,13 @@
     </row>
     <row r="11" spans="1:26" ht="17" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>611</v>
-      </c>
       <c r="C11" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>148</v>
@@ -19478,28 +19478,28 @@
         <v>314</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="M11" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>619</v>
       </c>
       <c r="N11" s="4">
         <v>2</v>
@@ -19530,13 +19530,13 @@
     </row>
     <row r="12" spans="1:26" ht="17" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>621</v>
-      </c>
       <c r="C12" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>141</v>
@@ -19545,28 +19545,28 @@
         <v>142</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>628</v>
-      </c>
       <c r="M12" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="N12" s="4">
         <v>2</v>
@@ -19597,13 +19597,13 @@
     </row>
     <row r="13" spans="1:26" ht="17" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>630</v>
-      </c>
       <c r="C13" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>150</v>
@@ -19612,28 +19612,28 @@
         <v>314</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>638</v>
       </c>
       <c r="N13" s="4">
         <v>2</v>
@@ -24959,11 +24959,11 @@
       <c r="P196" s="4"/>
       <c r="Q196" s="4"/>
       <c r="R196" s="7" t="str">
-        <f t="shared" ref="R196:R227" si="12">IF(A196="","",IFERROR(N196*O196*P196*Q196/20,0))</f>
+        <f t="shared" ref="R196:R203" si="12">IF(A196="","",IFERROR(N196*O196*P196*Q196/20,0))</f>
         <v/>
       </c>
       <c r="S196" s="8" t="str">
-        <f t="shared" ref="S196:S227" si="13">IF(R196="","",IF(R196&gt;=15,"Критический",IF(R196&gt;=9,"Высокий",IF(R196&gt;=5,"Средний",IF(R196&gt;=2,"Низкий","Отложить")))))</f>
+        <f t="shared" ref="S196:S203" si="13">IF(R196="","",IF(R196&gt;=15,"Критический",IF(R196&gt;=9,"Высокий",IF(R196&gt;=5,"Средний",IF(R196&gt;=2,"Низкий","Отложить")))))</f>
         <v/>
       </c>
       <c r="T196" s="4"/>
@@ -25341,46 +25341,46 @@
         <v>136</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M4" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>137</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="17" customHeight="1">
@@ -25388,422 +25388,422 @@
         <v>139</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>147</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="17" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>565</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>641</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J6" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M6" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>141</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>575</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>641</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J7" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="L7" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>141</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="17" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>585</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M8" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>137</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="17" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M9" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>137</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="17" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>602</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M10" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>137</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="17" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>611</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M11" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>148</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="17" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>621</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>641</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J12" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M12" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>141</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="17" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>630</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="M13" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>150</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="17" customHeight="1">
@@ -27573,19 +27573,19 @@
         <v>169</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>170</v>
@@ -27629,25 +27629,25 @@
         <v>172</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>651</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>652</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I5" s="4">
         <v>5</v>
@@ -27682,25 +27682,25 @@
     </row>
     <row r="6" spans="1:26" ht="17" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>655</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>657</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>658</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>336</v>
@@ -27738,25 +27738,25 @@
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>663</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>171</v>
@@ -27794,28 +27794,28 @@
     </row>
     <row r="8" spans="1:26" ht="17" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>664</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>665</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>170</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I8" s="4">
         <v>3</v>
@@ -27850,22 +27850,22 @@
     </row>
     <row r="9" spans="1:26" ht="17" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>670</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>671</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>170</v>
@@ -27906,22 +27906,22 @@
     </row>
     <row r="10" spans="1:26" ht="17" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>675</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>170</v>
@@ -27962,25 +27962,25 @@
     </row>
     <row r="11" spans="1:26" ht="17" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>679</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>171</v>
@@ -28018,25 +28018,25 @@
     </row>
     <row r="12" spans="1:26" ht="17" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>681</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>682</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>151</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>174</v>
@@ -28074,25 +28074,25 @@
     </row>
     <row r="13" spans="1:26" ht="17" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>686</v>
-      </c>
       <c r="G13" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>174</v>
@@ -28130,25 +28130,25 @@
     </row>
     <row r="14" spans="1:26" ht="17" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>688</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>689</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>151</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>174</v>
@@ -28186,25 +28186,25 @@
     </row>
     <row r="15" spans="1:26" ht="17" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>690</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>691</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>693</v>
-      </c>
       <c r="G15" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>174</v>
@@ -28242,25 +28242,25 @@
     </row>
     <row r="16" spans="1:26" ht="17" customHeight="1">
       <c r="A16" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>696</v>
-      </c>
       <c r="F16" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>174</v>
@@ -28298,25 +28298,25 @@
     </row>
     <row r="17" spans="1:17" ht="17" customHeight="1">
       <c r="A17" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>699</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>174</v>
@@ -28354,25 +28354,25 @@
     </row>
     <row r="18" spans="1:17" ht="17" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>703</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>704</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>336</v>
@@ -28410,25 +28410,25 @@
     </row>
     <row r="19" spans="1:17" ht="17" customHeight="1">
       <c r="A19" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>707</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>336</v>
@@ -28466,25 +28466,25 @@
     </row>
     <row r="20" spans="1:17" ht="17" customHeight="1">
       <c r="A20" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>708</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>709</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>336</v>
@@ -28522,25 +28522,25 @@
     </row>
     <row r="21" spans="1:17" ht="17" customHeight="1">
       <c r="A21" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>714</v>
-      </c>
       <c r="G21" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>336</v>
@@ -33462,15 +33462,15 @@
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
       <c r="M196" s="7" t="str">
-        <f t="shared" ref="M196:M227" si="18">IF(A196="","",IFERROR((I196+J196)*L196/K196,0))</f>
+        <f t="shared" ref="M196:M203" si="18">IF(A196="","",IFERROR((I196+J196)*L196/K196,0))</f>
         <v/>
       </c>
       <c r="N196" s="8" t="str">
-        <f t="shared" ref="N196:N227" si="19">IF(M196="","",IF(M196&gt;=16,"Критический",IF(M196&gt;=10,"Высокий",IF(M196&gt;=6,"Средний",IF(M196&gt;=3,"Низкий","Отложить")))))</f>
+        <f t="shared" ref="N196:N203" si="19">IF(M196="","",IF(M196&gt;=16,"Критический",IF(M196&gt;=10,"Высокий",IF(M196&gt;=6,"Средний",IF(M196&gt;=3,"Низкий","Отложить")))))</f>
         <v/>
       </c>
       <c r="O196" s="8" t="str">
-        <f t="shared" ref="O196:O227" si="20">IF(M196="","",IF(OR(N196="Критический",N196="Высокий"),"Да",IF(N196="Средний","Кандидат","Нет")))</f>
+        <f t="shared" ref="O196:O203" si="20">IF(M196="","",IF(OR(N196="Критический",N196="Высокий"),"Да",IF(N196="Средний","Кандидат","Нет")))</f>
         <v/>
       </c>
       <c r="P196" s="4"/>
@@ -33836,7 +33836,7 @@
         <v>187</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>188</v>
@@ -33874,7 +33874,7 @@
         <v>189</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="17" customHeight="1">
@@ -33882,16 +33882,16 @@
         <v>190</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>717</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>718</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>136</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F5" s="4">
         <v>5</v>
@@ -33920,24 +33920,24 @@
         <v>189</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="17" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>720</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -33966,24 +33966,24 @@
         <v>189</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>723</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F7" s="4">
         <v>3</v>
@@ -34012,24 +34012,24 @@
         <v>189</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="17" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>726</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F8" s="4">
         <v>4</v>
@@ -34058,24 +34058,24 @@
         <v>189</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="17" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>730</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F9" s="4">
         <v>5</v>
@@ -34101,27 +34101,27 @@
         <v>Проверить дополнительно</v>
       </c>
       <c r="M9" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="N9" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="17" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>734</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F10" s="4">
         <v>4</v>
@@ -34147,27 +34147,27 @@
         <v>Проверить дополнительно</v>
       </c>
       <c r="M10" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>735</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="17" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>738</v>
-      </c>
       <c r="C11" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>136</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F11" s="4">
         <v>4</v>
@@ -34193,10 +34193,10 @@
         <v>Исключить</v>
       </c>
       <c r="M11" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>739</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="17" customHeight="1">
@@ -38259,11 +38259,11 @@
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
       <c r="K196" s="7" t="str">
-        <f t="shared" ref="K196:K227" si="12">IF(A196="","",IFERROR((F196+G196+H196)*((6-J196)/5)/I196,0))</f>
+        <f t="shared" ref="K196:K203" si="12">IF(A196="","",IFERROR((F196+G196+H196)*((6-J196)/5)/I196,0))</f>
         <v/>
       </c>
       <c r="L196" s="8" t="str">
-        <f t="shared" ref="L196:L227" si="13">IF(K196="","",IF(K196&gt;=6,"Включить в первую версию",IF(K196&gt;=4,"Включить после проверки",IF(K196&gt;=2.5,"Проверить дополнительно",IF(K196&gt;=1.5,"Отложить","Исключить")))))</f>
+        <f t="shared" ref="L196:L203" si="13">IF(K196="","",IF(K196&gt;=6,"Включить в первую версию",IF(K196&gt;=4,"Включить после проверки",IF(K196&gt;=2.5,"Проверить дополнительно",IF(K196&gt;=1.5,"Отложить","Исключить")))))</f>
         <v/>
       </c>
       <c r="M196" s="4"/>
